--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -1829,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119727783</v>
+        <v>119726717</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,43 +1841,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590900</v>
+        <v>591152</v>
       </c>
       <c r="R13" t="n">
-        <v>6973729</v>
+        <v>6973788</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1936,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119726717</v>
+        <v>119727783</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,47 +1952,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591152</v>
+        <v>590900</v>
       </c>
       <c r="R14" t="n">
-        <v>6973788</v>
+        <v>6973729</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119726024</v>
+        <v>119726605</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,25 +2467,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591249</v>
+        <v>591127</v>
       </c>
       <c r="R19" t="n">
-        <v>6973875</v>
+        <v>6973805</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119726605</v>
+        <v>119726024</v>
       </c>
       <c r="B20" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,25 +2569,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591127</v>
+        <v>591249</v>
       </c>
       <c r="R20" t="n">
-        <v>6973805</v>
+        <v>6973875</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119724607</v>
+        <v>119724372</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,34 +1015,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590992</v>
+        <v>591035</v>
       </c>
       <c r="R5" t="n">
-        <v>6973819</v>
+        <v>6973680</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119724962</v>
+        <v>119724607</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,42 +1118,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591079</v>
+        <v>590992</v>
       </c>
       <c r="R6" t="n">
-        <v>6973923</v>
+        <v>6973819</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119724372</v>
+        <v>119724962</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,43 +1220,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591035</v>
+        <v>591079</v>
       </c>
       <c r="R7" t="n">
-        <v>6973680</v>
+        <v>6973923</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119728462</v>
+        <v>119727316</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591000</v>
+        <v>590941</v>
       </c>
       <c r="R2" t="n">
-        <v>6973673</v>
+        <v>6973616</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119726794</v>
+        <v>119727783</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,47 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591142</v>
+        <v>590900</v>
       </c>
       <c r="R3" t="n">
-        <v>6973748</v>
+        <v>6973729</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -893,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119724497</v>
+        <v>119725348</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97824</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,42 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591004</v>
+        <v>591264</v>
       </c>
       <c r="R4" t="n">
-        <v>6973746</v>
+        <v>6973946</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -999,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119724372</v>
+        <v>119724497</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,43 +998,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591035</v>
+        <v>591004</v>
       </c>
       <c r="R5" t="n">
-        <v>6973680</v>
+        <v>6973746</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1106,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119724607</v>
+        <v>119727774</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>96868</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,38 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590992</v>
+        <v>590894</v>
       </c>
       <c r="R6" t="n">
-        <v>6973819</v>
+        <v>6973738</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1208,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119724962</v>
+        <v>119726605</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,42 +1206,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591079</v>
+        <v>591127</v>
       </c>
       <c r="R7" t="n">
-        <v>6973923</v>
+        <v>6973805</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1314,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119726762</v>
+        <v>119727510</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>91832</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,34 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591135</v>
+        <v>590922</v>
       </c>
       <c r="R8" t="n">
-        <v>6973756</v>
+        <v>6973723</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1416,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119724713</v>
+        <v>119724607</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,39 +1414,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590988</v>
+        <v>590992</v>
       </c>
       <c r="R9" t="n">
-        <v>6973851</v>
+        <v>6973819</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1523,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119725348</v>
+        <v>119726762</v>
       </c>
       <c r="B10" t="n">
-        <v>97824</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591264</v>
+        <v>591135</v>
       </c>
       <c r="R10" t="n">
-        <v>6973946</v>
+        <v>6973756</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1625,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119726642</v>
+        <v>119726573</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1665,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591129</v>
+        <v>591132</v>
       </c>
       <c r="R11" t="n">
-        <v>6973800</v>
+        <v>6973851</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1727,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119726463</v>
+        <v>119726642</v>
       </c>
       <c r="B12" t="n">
-        <v>91254</v>
+        <v>90846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1739,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1767,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591175</v>
+        <v>591129</v>
       </c>
       <c r="R12" t="n">
-        <v>6973818</v>
+        <v>6973800</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1829,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119726717</v>
+        <v>119726463</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>91254</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,47 +1818,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591152</v>
+        <v>591175</v>
       </c>
       <c r="R13" t="n">
-        <v>6973788</v>
+        <v>6973818</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1940,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119727783</v>
+        <v>119727387</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1952,43 +1920,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590900</v>
+        <v>590934</v>
       </c>
       <c r="R14" t="n">
-        <v>6973729</v>
+        <v>6973642</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2047,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119727774</v>
+        <v>119726794</v>
       </c>
       <c r="B15" t="n">
-        <v>96868</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,38 +2022,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590894</v>
+        <v>591142</v>
       </c>
       <c r="R15" t="n">
-        <v>6973738</v>
+        <v>6973748</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2149,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119726069</v>
+        <v>119726717</v>
       </c>
       <c r="B16" t="n">
-        <v>96862</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,38 +2133,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591242</v>
+        <v>591152</v>
       </c>
       <c r="R16" t="n">
-        <v>6973874</v>
+        <v>6973788</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2251,10 +2232,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119726250</v>
+        <v>119726266</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,25 +2244,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591200</v>
+        <v>591205</v>
       </c>
       <c r="R17" t="n">
-        <v>6973827</v>
+        <v>6973816</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2353,10 +2334,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119727510</v>
+        <v>119726024</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,34 +2350,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590922</v>
+        <v>591249</v>
       </c>
       <c r="R18" t="n">
-        <v>6973723</v>
+        <v>6973875</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2455,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119726605</v>
+        <v>119728462</v>
       </c>
       <c r="B19" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,38 +2448,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591127</v>
+        <v>591000</v>
       </c>
       <c r="R19" t="n">
-        <v>6973805</v>
+        <v>6973673</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2557,7 +2543,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119726024</v>
+        <v>119728015</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2593,14 +2579,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591249</v>
+        <v>590907</v>
       </c>
       <c r="R20" t="n">
-        <v>6973875</v>
+        <v>6973847</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2659,10 +2645,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119726266</v>
+        <v>119724354</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,38 +2657,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591205</v>
+        <v>591039</v>
       </c>
       <c r="R21" t="n">
-        <v>6973816</v>
+        <v>6973646</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2761,10 +2752,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119727387</v>
+        <v>119724838</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,38 +2764,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590934</v>
+        <v>590979</v>
       </c>
       <c r="R22" t="n">
-        <v>6973642</v>
+        <v>6973876</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119724306</v>
+        <v>119724962</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,43 +2875,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591046</v>
+        <v>591079</v>
       </c>
       <c r="R23" t="n">
-        <v>6973632</v>
+        <v>6973923</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2970,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119724354</v>
+        <v>119726069</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>96862</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,43 +2981,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591039</v>
+        <v>591242</v>
       </c>
       <c r="R24" t="n">
-        <v>6973646</v>
+        <v>6973874</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3077,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119724838</v>
+        <v>119726250</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3089,47 +3083,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590979</v>
+        <v>591200</v>
       </c>
       <c r="R25" t="n">
-        <v>6973876</v>
+        <v>6973827</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3188,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119726573</v>
+        <v>119724372</v>
       </c>
       <c r="B26" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,34 +3189,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591132</v>
+        <v>591035</v>
       </c>
       <c r="R26" t="n">
-        <v>6973851</v>
+        <v>6973680</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3290,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119727316</v>
+        <v>119724306</v>
       </c>
       <c r="B27" t="n">
-        <v>91884</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3306,34 +3296,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590941</v>
+        <v>591046</v>
       </c>
       <c r="R27" t="n">
-        <v>6973616</v>
+        <v>6973632</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3392,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119728015</v>
+        <v>119724713</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3408,34 +3403,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590907</v>
+        <v>590988</v>
       </c>
       <c r="R28" t="n">
-        <v>6973847</v>
+        <v>6973851</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -3280,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119724306</v>
+        <v>119724713</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3296,16 +3296,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3316,7 +3316,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591046</v>
+        <v>590988</v>
       </c>
       <c r="R27" t="n">
-        <v>6973632</v>
+        <v>6973851</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119724713</v>
+        <v>119724306</v>
       </c>
       <c r="B28" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3403,16 +3403,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,7 +3423,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590988</v>
+        <v>591046</v>
       </c>
       <c r="R28" t="n">
-        <v>6973851</v>
+        <v>6973632</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119727316</v>
+        <v>119726794</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590941</v>
+        <v>591142</v>
       </c>
       <c r="R2" t="n">
-        <v>6973616</v>
+        <v>6973748</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119727783</v>
+        <v>119724838</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590900</v>
+        <v>590979</v>
       </c>
       <c r="R3" t="n">
-        <v>6973729</v>
+        <v>6973876</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -884,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119725348</v>
+        <v>119724607</v>
       </c>
       <c r="B4" t="n">
-        <v>97824</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591264</v>
+        <v>590992</v>
       </c>
       <c r="R4" t="n">
-        <v>6973946</v>
+        <v>6973819</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -986,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119724497</v>
+        <v>119725348</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97824</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,42 +1011,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591004</v>
+        <v>591264</v>
       </c>
       <c r="R5" t="n">
-        <v>6973746</v>
+        <v>6973946</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1092,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119727774</v>
+        <v>119724372</v>
       </c>
       <c r="B6" t="n">
-        <v>96868</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1113,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590894</v>
+        <v>591035</v>
       </c>
       <c r="R6" t="n">
-        <v>6973738</v>
+        <v>6973680</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1194,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119726605</v>
+        <v>119726024</v>
       </c>
       <c r="B7" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591127</v>
+        <v>591249</v>
       </c>
       <c r="R7" t="n">
-        <v>6973805</v>
+        <v>6973875</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1296,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119727510</v>
+        <v>119726642</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>90846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,34 +1326,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590922</v>
+        <v>591129</v>
       </c>
       <c r="R8" t="n">
-        <v>6973723</v>
+        <v>6973800</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1398,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119724607</v>
+        <v>119724306</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,34 +1428,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590992</v>
+        <v>591046</v>
       </c>
       <c r="R9" t="n">
-        <v>6973819</v>
+        <v>6973632</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1500,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119726762</v>
+        <v>119727316</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>91884</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,34 +1535,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591135</v>
+        <v>590941</v>
       </c>
       <c r="R10" t="n">
-        <v>6973756</v>
+        <v>6973616</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1602,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119726573</v>
+        <v>119726717</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,38 +1633,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591132</v>
+        <v>591152</v>
       </c>
       <c r="R11" t="n">
-        <v>6973851</v>
+        <v>6973788</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1704,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119726642</v>
+        <v>119728462</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,34 +1748,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591129</v>
+        <v>591000</v>
       </c>
       <c r="R12" t="n">
-        <v>6973800</v>
+        <v>6973673</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1806,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119726463</v>
+        <v>119726250</v>
       </c>
       <c r="B13" t="n">
-        <v>91254</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1851,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591175</v>
+        <v>591200</v>
       </c>
       <c r="R13" t="n">
-        <v>6973818</v>
+        <v>6973827</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1908,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119727387</v>
+        <v>119728015</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,38 +1953,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590934</v>
+        <v>590907</v>
       </c>
       <c r="R14" t="n">
-        <v>6973642</v>
+        <v>6973847</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2010,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119726794</v>
+        <v>119726266</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,47 +2055,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591142</v>
+        <v>591205</v>
       </c>
       <c r="R15" t="n">
-        <v>6973748</v>
+        <v>6973816</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2121,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119726717</v>
+        <v>119724713</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,47 +2157,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591152</v>
+        <v>590988</v>
       </c>
       <c r="R16" t="n">
-        <v>6973788</v>
+        <v>6973851</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2232,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119726266</v>
+        <v>119727510</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>91832</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2244,38 +2264,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591205</v>
+        <v>590922</v>
       </c>
       <c r="R17" t="n">
-        <v>6973816</v>
+        <v>6973723</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2334,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119726024</v>
+        <v>119726762</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2350,21 +2370,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2374,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591249</v>
+        <v>591135</v>
       </c>
       <c r="R18" t="n">
-        <v>6973875</v>
+        <v>6973756</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2436,10 +2456,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119728462</v>
+        <v>119726463</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2448,43 +2468,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591000</v>
+        <v>591175</v>
       </c>
       <c r="R19" t="n">
-        <v>6973673</v>
+        <v>6973818</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2543,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119728015</v>
+        <v>119726573</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2559,34 +2574,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590907</v>
+        <v>591132</v>
       </c>
       <c r="R20" t="n">
-        <v>6973847</v>
+        <v>6973851</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2752,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119724838</v>
+        <v>119727774</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>96868</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2764,47 +2779,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590979</v>
+        <v>590894</v>
       </c>
       <c r="R22" t="n">
-        <v>6973876</v>
+        <v>6973738</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3071,10 +3077,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119726250</v>
+        <v>119724497</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3083,38 +3089,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591200</v>
+        <v>591004</v>
       </c>
       <c r="R25" t="n">
-        <v>6973827</v>
+        <v>6973746</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3173,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119724372</v>
+        <v>119727387</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3185,43 +3195,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591035</v>
+        <v>590934</v>
       </c>
       <c r="R26" t="n">
-        <v>6973680</v>
+        <v>6973642</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3280,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119724713</v>
+        <v>119726605</v>
       </c>
       <c r="B27" t="n">
-        <v>57326</v>
+        <v>90527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3292,43 +3297,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590988</v>
+        <v>591127</v>
       </c>
       <c r="R27" t="n">
-        <v>6973851</v>
+        <v>6973805</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119724306</v>
+        <v>119727783</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3423,7 +3423,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591046</v>
+        <v>590900</v>
       </c>
       <c r="R28" t="n">
-        <v>6973632</v>
+        <v>6973729</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -3077,10 +3077,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119724497</v>
+        <v>119727783</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3089,42 +3089,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591004</v>
+        <v>590900</v>
       </c>
       <c r="R25" t="n">
-        <v>6973746</v>
+        <v>6973729</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3387,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119727783</v>
+        <v>119724497</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3399,43 +3400,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590900</v>
+        <v>591004</v>
       </c>
       <c r="R28" t="n">
-        <v>6973729</v>
+        <v>6973746</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119726794</v>
+        <v>119726642</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591142</v>
+        <v>591129</v>
       </c>
       <c r="R2" t="n">
-        <v>6973748</v>
+        <v>6973800</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119724838</v>
+        <v>119724354</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,47 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590979</v>
+        <v>591039</v>
       </c>
       <c r="R3" t="n">
-        <v>6973876</v>
+        <v>6973646</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -897,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119724607</v>
+        <v>119726573</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590992</v>
+        <v>591132</v>
       </c>
       <c r="R4" t="n">
-        <v>6973819</v>
+        <v>6973851</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -999,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119725348</v>
+        <v>119726024</v>
       </c>
       <c r="B5" t="n">
-        <v>97824</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591264</v>
+        <v>591249</v>
       </c>
       <c r="R5" t="n">
-        <v>6973946</v>
+        <v>6973875</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119724372</v>
+        <v>119724306</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1146,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591035</v>
+        <v>591046</v>
       </c>
       <c r="R6" t="n">
-        <v>6973680</v>
+        <v>6973632</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1208,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119726024</v>
+        <v>119727510</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591249</v>
+        <v>590922</v>
       </c>
       <c r="R7" t="n">
-        <v>6973875</v>
+        <v>6973723</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1310,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119726642</v>
+        <v>119726069</v>
       </c>
       <c r="B8" t="n">
-        <v>90846</v>
+        <v>96862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591129</v>
+        <v>591242</v>
       </c>
       <c r="R8" t="n">
-        <v>6973800</v>
+        <v>6973874</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1412,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119724306</v>
+        <v>119727774</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>96868</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,43 +1411,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591046</v>
+        <v>590894</v>
       </c>
       <c r="R9" t="n">
-        <v>6973632</v>
+        <v>6973738</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1519,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119727316</v>
+        <v>119726463</v>
       </c>
       <c r="B10" t="n">
-        <v>91884</v>
+        <v>91254</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,38 +1513,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590941</v>
+        <v>591175</v>
       </c>
       <c r="R10" t="n">
-        <v>6973616</v>
+        <v>6973818</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1621,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119726717</v>
+        <v>119727316</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,47 +1615,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591152</v>
+        <v>590941</v>
       </c>
       <c r="R11" t="n">
-        <v>6973788</v>
+        <v>6973616</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1732,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119728462</v>
+        <v>119726250</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,39 +1721,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591000</v>
+        <v>591200</v>
       </c>
       <c r="R12" t="n">
-        <v>6973673</v>
+        <v>6973827</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1839,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119726250</v>
+        <v>119726762</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591200</v>
+        <v>591135</v>
       </c>
       <c r="R13" t="n">
-        <v>6973827</v>
+        <v>6973756</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1941,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119728015</v>
+        <v>119724497</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1953,38 +1921,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590907</v>
+        <v>591004</v>
       </c>
       <c r="R14" t="n">
-        <v>6973847</v>
+        <v>6973746</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2043,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119726266</v>
+        <v>119728462</v>
       </c>
       <c r="B15" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2055,38 +2027,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591205</v>
+        <v>591000</v>
       </c>
       <c r="R15" t="n">
-        <v>6973816</v>
+        <v>6973673</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2145,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119724713</v>
+        <v>119724962</v>
       </c>
       <c r="B16" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,43 +2134,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590988</v>
+        <v>591079</v>
       </c>
       <c r="R16" t="n">
-        <v>6973851</v>
+        <v>6973923</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2252,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119727510</v>
+        <v>119727783</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,34 +2244,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590922</v>
+        <v>590900</v>
       </c>
       <c r="R17" t="n">
-        <v>6973723</v>
+        <v>6973729</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2354,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119726762</v>
+        <v>119724372</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,34 +2351,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591135</v>
+        <v>591035</v>
       </c>
       <c r="R18" t="n">
-        <v>6973756</v>
+        <v>6973680</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2456,10 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119726463</v>
+        <v>119726266</v>
       </c>
       <c r="B19" t="n">
-        <v>91254</v>
+        <v>90527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,21 +2458,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2496,10 +2482,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591175</v>
+        <v>591205</v>
       </c>
       <c r="R19" t="n">
-        <v>6973818</v>
+        <v>6973816</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2558,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119726573</v>
+        <v>119726717</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2570,38 +2556,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591132</v>
+        <v>591152</v>
       </c>
       <c r="R20" t="n">
-        <v>6973851</v>
+        <v>6973788</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2660,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119724354</v>
+        <v>119724838</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2672,43 +2667,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591039</v>
+        <v>590979</v>
       </c>
       <c r="R21" t="n">
-        <v>6973646</v>
+        <v>6973876</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2767,10 +2766,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119727774</v>
+        <v>119724713</v>
       </c>
       <c r="B22" t="n">
-        <v>96868</v>
+        <v>57326</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2779,38 +2778,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590894</v>
+        <v>590988</v>
       </c>
       <c r="R22" t="n">
-        <v>6973738</v>
+        <v>6973851</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2869,10 +2873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119724962</v>
+        <v>119725348</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>97824</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2881,42 +2885,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591079</v>
+        <v>591264</v>
       </c>
       <c r="R23" t="n">
-        <v>6973923</v>
+        <v>6973946</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119726069</v>
+        <v>119727387</v>
       </c>
       <c r="B24" t="n">
-        <v>96862</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,34 +2991,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591242</v>
+        <v>590934</v>
       </c>
       <c r="R24" t="n">
-        <v>6973874</v>
+        <v>6973642</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119727783</v>
+        <v>119728015</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3093,39 +3093,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590900</v>
+        <v>590907</v>
       </c>
       <c r="R25" t="n">
-        <v>6973729</v>
+        <v>6973847</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3184,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119727387</v>
+        <v>119726605</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3200,34 +3195,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590934</v>
+        <v>591127</v>
       </c>
       <c r="R26" t="n">
-        <v>6973642</v>
+        <v>6973805</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3286,10 +3281,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119726605</v>
+        <v>119724607</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3298,25 +3293,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3326,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591127</v>
+        <v>590992</v>
       </c>
       <c r="R27" t="n">
-        <v>6973805</v>
+        <v>6973819</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,7 +3383,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119724497</v>
+        <v>119726794</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3423,7 +3418,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591004</v>
+        <v>591142</v>
       </c>
       <c r="R28" t="n">
-        <v>6973746</v>
+        <v>6973748</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119724306</v>
+        <v>119727510</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591046</v>
+        <v>590922</v>
       </c>
       <c r="R6" t="n">
-        <v>6973632</v>
+        <v>6973723</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119727510</v>
+        <v>119724306</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,34 +1206,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590922</v>
+        <v>591046</v>
       </c>
       <c r="R7" t="n">
-        <v>6973723</v>
+        <v>6973632</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119727510</v>
+        <v>119724306</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590922</v>
+        <v>591046</v>
       </c>
       <c r="R6" t="n">
-        <v>6973723</v>
+        <v>6973632</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119724306</v>
+        <v>119727510</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591046</v>
+        <v>590922</v>
       </c>
       <c r="R7" t="n">
-        <v>6973632</v>
+        <v>6973723</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119726069</v>
+        <v>119726463</v>
       </c>
       <c r="B8" t="n">
-        <v>96862</v>
+        <v>91254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591242</v>
+        <v>591175</v>
       </c>
       <c r="R8" t="n">
-        <v>6973874</v>
+        <v>6973818</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119727774</v>
+        <v>119727316</v>
       </c>
       <c r="B9" t="n">
-        <v>96868</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590894</v>
+        <v>590941</v>
       </c>
       <c r="R9" t="n">
-        <v>6973738</v>
+        <v>6973616</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119726463</v>
+        <v>119726069</v>
       </c>
       <c r="B10" t="n">
-        <v>91254</v>
+        <v>96862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591175</v>
+        <v>591242</v>
       </c>
       <c r="R10" t="n">
-        <v>6973818</v>
+        <v>6973874</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119727316</v>
+        <v>119727774</v>
       </c>
       <c r="B11" t="n">
-        <v>91884</v>
+        <v>96868</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590941</v>
+        <v>590894</v>
       </c>
       <c r="R11" t="n">
-        <v>6973616</v>
+        <v>6973738</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119726266</v>
+        <v>119726717</v>
       </c>
       <c r="B19" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,38 +2454,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591205</v>
+        <v>591152</v>
       </c>
       <c r="R19" t="n">
-        <v>6973816</v>
+        <v>6973788</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2544,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119726717</v>
+        <v>119726266</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,47 +2565,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591152</v>
+        <v>591205</v>
       </c>
       <c r="R20" t="n">
-        <v>6973788</v>
+        <v>6973816</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119724306</v>
+        <v>119727510</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591046</v>
+        <v>590922</v>
       </c>
       <c r="R6" t="n">
-        <v>6973632</v>
+        <v>6973723</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119727510</v>
+        <v>119724306</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,34 +1206,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590922</v>
+        <v>591046</v>
       </c>
       <c r="R7" t="n">
-        <v>6973723</v>
+        <v>6973632</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119727783</v>
+        <v>119724372</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2264,7 +2264,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590900</v>
+        <v>591035</v>
       </c>
       <c r="R17" t="n">
-        <v>6973729</v>
+        <v>6973680</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119724372</v>
+        <v>119726266</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,43 +2347,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591035</v>
+        <v>591205</v>
       </c>
       <c r="R18" t="n">
-        <v>6973680</v>
+        <v>6973816</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2553,10 +2548,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119726266</v>
+        <v>119724838</v>
       </c>
       <c r="B20" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2565,38 +2560,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591205</v>
+        <v>590979</v>
       </c>
       <c r="R20" t="n">
-        <v>6973816</v>
+        <v>6973876</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2655,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119724838</v>
+        <v>119725348</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>97824</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2667,47 +2671,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590979</v>
+        <v>591264</v>
       </c>
       <c r="R21" t="n">
-        <v>6973876</v>
+        <v>6973946</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2873,10 +2868,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119725348</v>
+        <v>119727387</v>
       </c>
       <c r="B23" t="n">
-        <v>97824</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,34 +2884,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591264</v>
+        <v>590934</v>
       </c>
       <c r="R23" t="n">
-        <v>6973946</v>
+        <v>6973642</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2975,10 +2970,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119727387</v>
+        <v>119728015</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,38 +2982,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590934</v>
+        <v>590907</v>
       </c>
       <c r="R24" t="n">
-        <v>6973642</v>
+        <v>6973847</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3077,10 +3072,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119728015</v>
+        <v>119726605</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3089,38 +3084,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590907</v>
+        <v>591127</v>
       </c>
       <c r="R25" t="n">
-        <v>6973847</v>
+        <v>6973805</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3179,10 +3174,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119726605</v>
+        <v>119724607</v>
       </c>
       <c r="B26" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3191,25 +3186,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591127</v>
+        <v>590992</v>
       </c>
       <c r="R26" t="n">
-        <v>6973805</v>
+        <v>6973819</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3281,10 +3276,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119724607</v>
+        <v>119726794</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3293,38 +3288,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590992</v>
+        <v>591142</v>
       </c>
       <c r="R27" t="n">
-        <v>6973819</v>
+        <v>6973748</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3383,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119726794</v>
+        <v>119725191</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3395,47 +3399,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591142</v>
+        <v>591147</v>
       </c>
       <c r="R28" t="n">
-        <v>6973748</v>
+        <v>6973964</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3494,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119725191</v>
+        <v>119926828</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3510,37 +3505,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591147</v>
+        <v>591026</v>
       </c>
       <c r="R29" t="n">
-        <v>6973964</v>
+        <v>6973642</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119926828</v>
+        <v>119926655</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3608,43 +3608,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591026</v>
+        <v>591087</v>
       </c>
       <c r="R30" t="n">
-        <v>6973642</v>
+        <v>6973649</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3703,53 +3698,61 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119926655</v>
+        <v>119727783</v>
       </c>
       <c r="B31" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dialog hos validator</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591087</v>
+        <v>590900</v>
       </c>
       <c r="R31" t="n">
-        <v>6973649</v>
+        <v>6973729</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,12 +3776,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119726266</v>
+        <v>119726717</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,38 +2347,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591205</v>
+        <v>591152</v>
       </c>
       <c r="R18" t="n">
-        <v>6973816</v>
+        <v>6973788</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2437,10 +2446,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119726717</v>
+        <v>119726266</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,47 +2458,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591152</v>
+        <v>591205</v>
       </c>
       <c r="R19" t="n">
-        <v>6973788</v>
+        <v>6973816</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119725348</v>
+        <v>119724713</v>
       </c>
       <c r="B21" t="n">
-        <v>97824</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,38 +2671,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591264</v>
+        <v>590988</v>
       </c>
       <c r="R21" t="n">
-        <v>6973946</v>
+        <v>6973851</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2761,10 +2766,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119724713</v>
+        <v>119725348</v>
       </c>
       <c r="B22" t="n">
-        <v>57326</v>
+        <v>97824</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,43 +2778,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590988</v>
+        <v>591264</v>
       </c>
       <c r="R22" t="n">
-        <v>6973851</v>
+        <v>6973946</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119726717</v>
+        <v>119726266</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,47 +2347,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591152</v>
+        <v>591205</v>
       </c>
       <c r="R18" t="n">
-        <v>6973788</v>
+        <v>6973816</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2446,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119726266</v>
+        <v>119726717</v>
       </c>
       <c r="B19" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2458,38 +2449,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591205</v>
+        <v>591152</v>
       </c>
       <c r="R19" t="n">
-        <v>6973816</v>
+        <v>6973788</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119726642</v>
+        <v>119727387</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591129</v>
+        <v>590934</v>
       </c>
       <c r="R2" t="n">
-        <v>6973800</v>
+        <v>6973642</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119724354</v>
+        <v>119728015</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591039</v>
+        <v>590907</v>
       </c>
       <c r="R3" t="n">
-        <v>6973646</v>
+        <v>6973847</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -887,7 +882,7 @@
         <v>119726573</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119726024</v>
+        <v>119724372</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591249</v>
+        <v>591035</v>
       </c>
       <c r="R5" t="n">
-        <v>6973875</v>
+        <v>6973680</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119727510</v>
+        <v>119724354</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590922</v>
+        <v>591039</v>
       </c>
       <c r="R6" t="n">
-        <v>6973723</v>
+        <v>6973646</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119724306</v>
+        <v>119724838</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,43 +1207,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591046</v>
+        <v>590979</v>
       </c>
       <c r="R7" t="n">
-        <v>6973632</v>
+        <v>6973876</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119726463</v>
+        <v>119726024</v>
       </c>
       <c r="B8" t="n">
-        <v>91254</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1318,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591175</v>
+        <v>591249</v>
       </c>
       <c r="R8" t="n">
-        <v>6973818</v>
+        <v>6973875</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119727316</v>
+        <v>119724607</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,34 +1424,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590941</v>
+        <v>590992</v>
       </c>
       <c r="R9" t="n">
-        <v>6973616</v>
+        <v>6973819</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119726069</v>
+        <v>119726266</v>
       </c>
       <c r="B10" t="n">
-        <v>96862</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591242</v>
+        <v>591205</v>
       </c>
       <c r="R10" t="n">
-        <v>6973874</v>
+        <v>6973816</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119727774</v>
+        <v>119724962</v>
       </c>
       <c r="B11" t="n">
-        <v>96868</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1624,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590894</v>
+        <v>591079</v>
       </c>
       <c r="R11" t="n">
-        <v>6973738</v>
+        <v>6973923</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1705,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119726250</v>
+        <v>119726605</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>90545</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1730,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591200</v>
+        <v>591127</v>
       </c>
       <c r="R12" t="n">
-        <v>6973827</v>
+        <v>6973805</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1807,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119726762</v>
+        <v>119726794</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,38 +1832,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591135</v>
+        <v>591142</v>
       </c>
       <c r="R13" t="n">
-        <v>6973756</v>
+        <v>6973748</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1909,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119724497</v>
+        <v>119726642</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,42 +1943,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591004</v>
+        <v>591129</v>
       </c>
       <c r="R14" t="n">
-        <v>6973746</v>
+        <v>6973800</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2015,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119728462</v>
+        <v>119724713</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,16 +2049,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2051,7 +2069,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2060,10 +2078,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591000</v>
+        <v>590988</v>
       </c>
       <c r="R15" t="n">
-        <v>6973673</v>
+        <v>6973851</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2122,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119724962</v>
+        <v>119724306</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,42 +2152,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591079</v>
+        <v>591046</v>
       </c>
       <c r="R16" t="n">
-        <v>6973923</v>
+        <v>6973632</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2228,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119724372</v>
+        <v>119727510</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>91850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2244,39 +2263,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591035</v>
+        <v>590922</v>
       </c>
       <c r="R17" t="n">
-        <v>6973680</v>
+        <v>6973723</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2335,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119726266</v>
+        <v>119724497</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,38 +2361,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591205</v>
+        <v>591004</v>
       </c>
       <c r="R18" t="n">
-        <v>6973816</v>
+        <v>6973746</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2437,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119726717</v>
+        <v>119726762</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,47 +2467,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591152</v>
+        <v>591135</v>
       </c>
       <c r="R19" t="n">
-        <v>6973788</v>
+        <v>6973756</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2548,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119724838</v>
+        <v>119727774</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>96891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2560,47 +2569,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590979</v>
+        <v>590894</v>
       </c>
       <c r="R20" t="n">
-        <v>6973876</v>
+        <v>6973738</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119724713</v>
+        <v>119727316</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>91902</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,39 +2675,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590988</v>
+        <v>590941</v>
       </c>
       <c r="R21" t="n">
-        <v>6973851</v>
+        <v>6973616</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2766,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119725348</v>
+        <v>119726717</v>
       </c>
       <c r="B22" t="n">
-        <v>97824</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2778,38 +2773,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591264</v>
+        <v>591152</v>
       </c>
       <c r="R22" t="n">
-        <v>6973946</v>
+        <v>6973788</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2868,10 +2872,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119727387</v>
+        <v>119726069</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>96885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2884,34 +2888,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590934</v>
+        <v>591242</v>
       </c>
       <c r="R23" t="n">
-        <v>6973642</v>
+        <v>6973874</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2970,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119728015</v>
+        <v>119726250</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2986,34 +2990,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590907</v>
+        <v>591200</v>
       </c>
       <c r="R24" t="n">
-        <v>6973847</v>
+        <v>6973827</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3072,10 +3076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119726605</v>
+        <v>119728462</v>
       </c>
       <c r="B25" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3084,38 +3088,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591127</v>
+        <v>591000</v>
       </c>
       <c r="R25" t="n">
-        <v>6973805</v>
+        <v>6973673</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3174,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119724607</v>
+        <v>119726463</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>91272</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3186,25 +3195,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3214,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590992</v>
+        <v>591175</v>
       </c>
       <c r="R26" t="n">
-        <v>6973819</v>
+        <v>6973818</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3276,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119726794</v>
+        <v>119725348</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>97847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3288,47 +3297,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591142</v>
+        <v>591264</v>
       </c>
       <c r="R27" t="n">
-        <v>6973748</v>
+        <v>6973946</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3390,7 +3390,7 @@
         <v>119725191</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119926828</v>
+        <v>119926655</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3501,43 +3501,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591026</v>
+        <v>591087</v>
       </c>
       <c r="R29" t="n">
-        <v>6973642</v>
+        <v>6973649</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3596,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119926655</v>
+        <v>119926828</v>
       </c>
       <c r="B30" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3608,38 +3603,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591087</v>
+        <v>591026</v>
       </c>
       <c r="R30" t="n">
-        <v>6973649</v>
+        <v>6973642</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3701,7 +3701,7 @@
         <v>119727783</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119926655</v>
+        <v>119926828</v>
       </c>
       <c r="B29" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3501,38 +3501,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591087</v>
+        <v>591026</v>
       </c>
       <c r="R29" t="n">
-        <v>6973649</v>
+        <v>6973642</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3591,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119926828</v>
+        <v>119926655</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3603,43 +3608,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591026</v>
+        <v>591087</v>
       </c>
       <c r="R30" t="n">
-        <v>6973642</v>
+        <v>6973649</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -3489,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119926828</v>
+        <v>119926655</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3501,43 +3501,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591026</v>
+        <v>591087</v>
       </c>
       <c r="R29" t="n">
-        <v>6973642</v>
+        <v>6973649</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3596,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119926655</v>
+        <v>119926828</v>
       </c>
       <c r="B30" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3608,38 +3603,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591087</v>
+        <v>591026</v>
       </c>
       <c r="R30" t="n">
-        <v>6973649</v>
+        <v>6973642</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>119724372</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>119724354</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>119724306</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>119728462</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>119926828</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>119727783</v>
       </c>
       <c r="B31" t="n">
-        <v>57333</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>119724372</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>119724354</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>119724306</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>119728462</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>119926828</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>119727783</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>119724372</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>119724354</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>119724306</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>119728462</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>119926828</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>119727783</v>
       </c>
       <c r="B31" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>119724372</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>119724354</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>119724306</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>119728462</v>
       </c>
       <c r="B25" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>119926828</v>
       </c>
       <c r="B30" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>119727783</v>
       </c>
       <c r="B31" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119727387</v>
+        <v>119726642</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590934</v>
+        <v>591129</v>
       </c>
       <c r="R2" t="n">
-        <v>6973642</v>
+        <v>6973800</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119728015</v>
+        <v>119726250</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590907</v>
+        <v>591200</v>
       </c>
       <c r="R3" t="n">
-        <v>6973847</v>
+        <v>6973827</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -882,12 +872,7 @@
         <v>119726573</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119724372</v>
+        <v>119727054</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,39 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591035</v>
+        <v>591130</v>
       </c>
       <c r="R5" t="n">
-        <v>6973680</v>
+        <v>6973633</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,55 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119724354</v>
+        <v>119726463</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591039</v>
+        <v>591175</v>
       </c>
       <c r="R6" t="n">
-        <v>6973646</v>
+        <v>6973818</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,59 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119724838</v>
+        <v>119727510</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590979</v>
+        <v>590922</v>
       </c>
       <c r="R7" t="n">
-        <v>6973876</v>
+        <v>6973723</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1306,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119726024</v>
+        <v>119727387</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591249</v>
+        <v>590934</v>
       </c>
       <c r="R8" t="n">
-        <v>6973875</v>
+        <v>6973642</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1408,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119724607</v>
+        <v>119726266</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590992</v>
+        <v>591205</v>
       </c>
       <c r="R9" t="n">
-        <v>6973819</v>
+        <v>6973816</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1510,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119726266</v>
+        <v>119726605</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591205</v>
+        <v>591127</v>
       </c>
       <c r="R10" t="n">
-        <v>6973816</v>
+        <v>6973805</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1612,57 +1548,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119724962</v>
+        <v>119926655</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591079</v>
+        <v>591087</v>
       </c>
       <c r="R11" t="n">
-        <v>6973923</v>
+        <v>6973649</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1686,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119726605</v>
+        <v>119724607</v>
       </c>
       <c r="B12" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1758,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591127</v>
+        <v>590992</v>
       </c>
       <c r="R12" t="n">
-        <v>6973805</v>
+        <v>6973819</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1820,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119726794</v>
+        <v>119725191</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,43 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591142</v>
+        <v>591147</v>
       </c>
       <c r="R13" t="n">
-        <v>6973748</v>
+        <v>6973964</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1931,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119726642</v>
+        <v>119726024</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591129</v>
+        <v>591249</v>
       </c>
       <c r="R14" t="n">
-        <v>6973800</v>
+        <v>6973875</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2033,55 +1936,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119724713</v>
+        <v>119728015</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Norr-Nysjöberget, Norr-Nysjöberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590988</v>
+        <v>590907</v>
       </c>
       <c r="R15" t="n">
-        <v>6973851</v>
+        <v>6973847</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2140,32 +2033,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119724306</v>
+        <v>119724713</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2176,7 +2064,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2185,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591046</v>
+        <v>590988</v>
       </c>
       <c r="R16" t="n">
-        <v>6973632</v>
+        <v>6973851</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2247,15 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119727510</v>
+        <v>119724306</v>
       </c>
       <c r="B17" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2263,34 +2146,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590922</v>
+        <v>591046</v>
       </c>
       <c r="R17" t="n">
-        <v>6973723</v>
+        <v>6973632</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2349,54 +2237,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119724497</v>
+        <v>119724354</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591004</v>
+        <v>591039</v>
       </c>
       <c r="R18" t="n">
-        <v>6973746</v>
+        <v>6973646</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2455,15 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119726762</v>
+        <v>119724372</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,34 +2350,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591135</v>
+        <v>591035</v>
       </c>
       <c r="R19" t="n">
-        <v>6973756</v>
+        <v>6973680</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2557,50 +2441,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119727774</v>
+        <v>119725579</v>
       </c>
       <c r="B20" t="n">
-        <v>96891</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590894</v>
+        <v>591249</v>
       </c>
       <c r="R20" t="n">
-        <v>6973738</v>
+        <v>6973972</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2659,15 +2546,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119727316</v>
+        <v>119727783</v>
       </c>
       <c r="B21" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2675,34 +2557,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590941</v>
+        <v>590900</v>
       </c>
       <c r="R21" t="n">
-        <v>6973616</v>
+        <v>6973729</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2761,59 +2651,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119726717</v>
+        <v>119728462</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591152</v>
+        <v>591000</v>
       </c>
       <c r="R22" t="n">
-        <v>6973788</v>
+        <v>6973673</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2872,53 +2753,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119726069</v>
+        <v>119926828</v>
       </c>
       <c r="B23" t="n">
-        <v>96885</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
+          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591242</v>
+        <v>591026</v>
       </c>
       <c r="R23" t="n">
-        <v>6973874</v>
+        <v>6973642</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2942,12 +2823,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,37 +2855,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119726250</v>
+        <v>119725348</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3014,10 +2890,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591200</v>
+        <v>591264</v>
       </c>
       <c r="R24" t="n">
-        <v>6973827</v>
+        <v>6973946</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3076,55 +2952,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119728462</v>
+        <v>119724497</v>
       </c>
       <c r="B25" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591000</v>
+        <v>591004</v>
       </c>
       <c r="R25" t="n">
-        <v>6973673</v>
+        <v>6973746</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3183,50 +3053,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119726463</v>
+        <v>119724838</v>
       </c>
       <c r="B26" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591175</v>
+        <v>590979</v>
       </c>
       <c r="R26" t="n">
-        <v>6973818</v>
+        <v>6973876</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3285,50 +3159,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119725348</v>
+        <v>119724962</v>
       </c>
       <c r="B27" t="n">
-        <v>97847</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591264</v>
+        <v>591079</v>
       </c>
       <c r="R27" t="n">
-        <v>6973946</v>
+        <v>6973923</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3387,50 +3260,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119725191</v>
+        <v>119726717</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591147</v>
+        <v>591152</v>
       </c>
       <c r="R28" t="n">
-        <v>6973964</v>
+        <v>6973788</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3489,53 +3366,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119926655</v>
+        <v>119726794</v>
       </c>
       <c r="B29" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591087</v>
+        <v>591142</v>
       </c>
       <c r="R29" t="n">
-        <v>6973649</v>
+        <v>6973748</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3559,12 +3440,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3591,58 +3472,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119926828</v>
+        <v>119727774</v>
       </c>
       <c r="B30" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Bergändtjärnen, Bergändtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591026</v>
+        <v>590894</v>
       </c>
       <c r="R30" t="n">
-        <v>6973642</v>
+        <v>6973738</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3666,12 +3537,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3698,58 +3569,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119727783</v>
+        <v>119726069</v>
       </c>
       <c r="B31" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Dialog hos validator</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster-Krokmyrsjön, Liden, Väster-Krokmyrsjön, Liden, Mpd</t>
+          <t>Väster-Krokmyrsjön, Väster-Krokmyrsjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590900</v>
+        <v>591242</v>
       </c>
       <c r="R31" t="n">
-        <v>6973729</v>
+        <v>6973874</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>

--- a/artfynd/A 30473-2024 artfynd.xlsx
+++ b/artfynd/A 30473-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726642</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726250</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726573</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119727054</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726463</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119727510</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119727387</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726266</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726605</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119926655</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724607</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119725191</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726024</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119728015</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724713</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724306</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724354</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724372</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2543,6 +2638,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119725579</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2648,6 +2748,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119727783</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2750,6 +2855,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119728462</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2852,6 +2962,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119926828</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2949,6 +3064,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119725348</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3050,6 +3170,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724497</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3156,6 +3281,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724838</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3257,6 +3387,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724962</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3363,6 +3498,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726717</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3469,6 +3609,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726794</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3566,6 +3711,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119727774</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3663,8 +3813,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119726069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>